--- a/june 2026/LMT_JUNE_26/Jalal Sons/Jalal Sons Behria Orchard.xlsx
+++ b/june 2026/LMT_JUNE_26/Jalal Sons/Jalal Sons Behria Orchard.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85473F6B-5B29-4C27-B135-F85AF284F732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E4C21-78D4-4351-954B-6F0119DEF01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3347,7 +3347,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -3375,7 +3375,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -4568,7 +4568,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -4596,7 +4596,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -5789,7 +5789,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -5817,7 +5817,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -7010,7 +7010,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -7038,7 +7038,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -8231,7 +8231,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -8259,7 +8259,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -9452,7 +9452,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -9480,7 +9480,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -10670,7 +10670,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -10698,7 +10698,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -11887,7 +11887,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -11915,7 +11915,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -13104,7 +13104,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -13132,7 +13132,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -14321,7 +14321,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -14349,7 +14349,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -18288,7 +18288,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -18316,7 +18316,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -19505,7 +19505,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -19533,7 +19533,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -20722,7 +20722,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -20750,7 +20750,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -21939,7 +21939,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -21967,7 +21967,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -23162,7 +23162,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -23190,7 +23190,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -24629,7 +24629,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -24657,7 +24657,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -25828,7 +25828,7 @@
       <c r="L3" s="200"/>
       <c r="M3" s="200"/>
       <c r="N3" s="199">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="O3" s="199"/>
       <c r="P3" s="199"/>
@@ -25855,8 +25855,7 @@
       <c r="L4" s="200"/>
       <c r="M4" s="200"/>
       <c r="N4" s="201">
-        <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -25883,8 +25882,8 @@
       <c r="L5" s="200"/>
       <c r="M5" s="200"/>
       <c r="N5" s="201">
-        <f ca="1">N4-1</f>
-        <v>46215</v>
+        <f>N4-1</f>
+        <v>46201</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -27083,7 +27082,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -27111,7 +27110,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -28303,7 +28302,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -28331,7 +28330,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -29524,7 +29523,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -29552,7 +29551,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -30745,7 +30744,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -30773,7 +30772,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
